--- a/assets/constructions/examples/ctd_tsmb_chamfer_preparting.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_chamfer_preparting.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK6"/>
+  <dimension ref="A1:AP6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,25 +614,58 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BH45.044215.LETC</t>
+          <t>M552PPW100L25RVBX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BRICE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>VARGUS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Microscope</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VAR_M4</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>VAR_M5</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>PMKNSH</t>
@@ -640,51 +673,53 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>3.88</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
       <c r="L2" t="n">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
       <c r="M2" t="n">
-        <v>3.95</v>
+        <v>4.94</v>
       </c>
       <c r="N2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>0.2</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>18.4</v>
+        <v>28.15</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>45</v>
-      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>VARGUS_D:4</t>
+          <t>VARGUS_D:5</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -721,11 +756,30 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>38.93</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AO2" t="n">
+        <v>3578.98</v>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BTPPW100.055225.LETC</t>
+          <t>BTPPW100.055215.LETC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -765,11 +819,11 @@
         <v>4.94</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="Q3" t="n">
         <v>0.7</v>
@@ -784,7 +838,7 @@
         </is>
       </c>
       <c r="U3" t="n">
-        <v>28.15</v>
+        <v>18.15</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
@@ -830,11 +884,30 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>4836.98</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AO3" t="n">
+        <v>4836.98</v>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M552PPW100L20RVBX</t>
+          <t>M552CH4545L20R VBX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -870,42 +943,40 @@
         <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
+        <v>3.7</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="M4" t="n">
-        <v>4.94</v>
+        <v>4.95</v>
       </c>
       <c r="N4" t="n">
         <v>20</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
+        <v>46.2</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0.2</v>
+      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>23.15</v>
+        <v>23.35</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>45</v>
+      </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
@@ -947,11 +1018,30 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AO4" t="n">
+        <v>3548.64</v>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M772CH4545L40R VBX</t>
+          <t>M772CH4545L20L VBX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -997,11 +1087,11 @@
         <v>6.95</v>
       </c>
       <c r="N5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>66.2</v>
+        <v>51.2</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -1010,11 +1100,11 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>41.6</v>
+        <v>26.6</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
@@ -1062,11 +1152,30 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AO5" t="n">
+        <v>2960.27</v>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M552CH4545L20R VBX</t>
+          <t>M552PPW100L20RC VTX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1102,40 +1211,42 @@
         <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
+        <v>3.88</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
       <c r="L6" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="M6" t="n">
-        <v>4.95</v>
+        <v>4.94</v>
       </c>
       <c r="N6" t="n">
         <v>20</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
-        <v>0.2</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>23.35</v>
+        <v>23.15</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="n">
-        <v>45</v>
-      </c>
+      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
@@ -1150,12 +1261,12 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>VBX</t>
+          <t>VTX</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
@@ -1175,6 +1286,25 @@
       <c r="AK6" t="inlineStr">
         <is>
           <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AO6" t="n">
+        <v>4008.31</v>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
